--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3510,6 +3510,63 @@
     </rPh>
     <rPh sb="120" eb="122">
       <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・人形状のモデルが動かせるとわかりやすい技術アピールになるので重要です。
+・指定の空オブジェクトを目指す仕組みができると、いろいろな演出に応用が効きそうですね。汎用的な仕組みを目指せるとさらに良いです。</t>
+    <rPh sb="1" eb="4">
+      <t>ヒトケイジョウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>エンシュツ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>オウヨウ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="80" eb="83">
+      <t>ハンヨウテキ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シク</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>メザ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ヨ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4573,8 +4630,12 @@
       <c r="C6" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
       <c r="A7" s="12"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="80">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3567,6 +3567,25 @@
     </rPh>
     <rPh sb="96" eb="97">
       <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業報告と翌日の作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウホウコク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4641,8 +4660,12 @@
       <c r="A7" s="12"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
       <c r="A8" s="12"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13425" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7905" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3567,6 +3567,196 @@
     </rPh>
     <rPh sb="96" eb="97">
       <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業報告と翌日の作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウホウコク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NPC行動スクリプトは設置した経由地点オブジェクトをインスペクターに順番に追加することで順番通りに歩くようなスクリプトが完成した。
+NPC缶蹴りスクリプトはレイヤーを用いて缶を感知する用の当たり判定レイヤーと経由地点に到着時したことを感知する用の当たり判定レイヤーの二つを作り、缶(タグ)が来たらキックアニメーションを再生するスクリプトの制作で、完成して実際にアタッチしたら女性NPCだけ正常に動作ししなかったので次回はそれの修正。</t>
+    <rPh sb="3" eb="5">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ケイユチテン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジュンバン</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ドオ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>アル</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>カンケ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>カンチ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="104" eb="108">
+      <t>ケイユチテン</t>
+    </rPh>
+    <rPh sb="109" eb="112">
+      <t>トウチャクジ</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>カンチ</t>
+    </rPh>
+    <rPh sb="121" eb="122">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>フタ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="169" eb="171">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="173" eb="175">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="187" eb="189">
+      <t>ジョセイ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="197" eb="199">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t>ジカイ</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPC行動スクリプトの制作
+・NPC缶蹴りスクリプトの制作</t>
+    <rPh sb="4" eb="6">
+      <t>コウドウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンケ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPC缶蹴りスクリプトの修正</t>
+    <rPh sb="4" eb="6">
+      <t>カンケ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原因が判明し修正して完成したので、男性NPC・女性NPC・子供NPC・経由地点オブジェクトの原型プレハブを生成し、パッケージをエクスポートした。</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンメイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ダンセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジョセイ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>コドモ</t>
+    </rPh>
+    <rPh sb="35" eb="39">
+      <t>ケイユチテン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ゲンケイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セイセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4638,16 +4828,32 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="12">
+        <v>46122</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="12"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
+      <c r="A8" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="13"/>
     </row>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3758,6 +3758,10 @@
     <rPh sb="53" eb="55">
       <t>セイセイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4854,7 +4858,9 @@
       <c r="C8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -3717,17 +3717,29 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・NPC缶蹴りスクリプトの修正</t>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・NPC缶蹴りスクリプトの修正
+・自販機スクリプトの制作</t>
     <rPh sb="4" eb="6">
       <t>カンケ</t>
     </rPh>
     <rPh sb="13" eb="15">
       <t>シュウセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>原因が判明し修正して完成したので、男性NPC・女性NPC・子供NPC・経由地点オブジェクトの原型プレハブを生成し、パッケージをエクスポートした。</t>
+    <rPh sb="17" eb="20">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原因が判明し修正して完成したので、男性NPC・女性NPC・子供NPC・経由地点オブジェクトの原型プレハブを生成し、パッケージをエクスポートした。
+自販機に缶(タグ)が近づくとUIが表示され、UI表示中に[F]入力でコインを消費するスクリプトを制作中。</t>
     <rPh sb="0" eb="2">
       <t>ゲンイン</t>
     </rPh>
@@ -3758,10 +3770,36 @@
     <rPh sb="53" eb="55">
       <t>セイセイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <rPh sb="73" eb="76">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>チュウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4853,13 +4891,13 @@
         <v>46125</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>84</v>
       </c>
       <c r="E8" s="13"/>
     </row>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3717,10 +3717,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・NPC缶蹴りスクリプトの修正
 ・自販機スクリプトの制作</t>
     <rPh sb="4" eb="6">
@@ -3799,6 +3795,45 @@
     </rPh>
     <rPh sb="123" eb="124">
       <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業報告と翌日の作業予定の記載をお願いします。
+　この報告の場合は B9 
+　明日の報告であれば B10 セルを前日に記入してください。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウホウコク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ゼンジツ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キニュウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4891,15 +4926,17 @@
         <v>46125</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
       <c r="A9" s="12"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7905" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3717,10 +3717,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・NPC缶蹴りスクリプトの修正
 ・自販機スクリプトの制作</t>
     <rPh sb="4" eb="6">
@@ -3799,6 +3795,131 @@
     </rPh>
     <rPh sb="123" eb="124">
       <t>チュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業報告と翌日の作業予定の記載をお願いします。
+　この報告の場合は B9 
+　明日の報告であれば B10 セルを前日に記入してください。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウホウコク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>サギョウヨテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ネガ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ホウコク</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ゼンジツ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>キニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機スクリプトの制作
+・選択肢UIスクリプトの制作</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの制作</t>
+    <rPh sb="1" eb="4">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自販機スクリプトのが完成したので、その続きで[F]入力で能力の選択肢UIが出るようにし、カーソルが乗ると選択肢の周りが黄色く表示されて、クリックするとDebug.Logが表示される選択肢UIスクリプトを制作中。
+イベントトリガーがごちゃごちゃにならないように気を付ける。</t>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="52" eb="55">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>キイロ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="90" eb="93">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="129" eb="130">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4891,26 +5012,38 @@
         <v>46125</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="13"/>
     </row>
     <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
+      <c r="A9" s="12">
+        <v>46126</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="12"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="12">
+        <v>46127</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="C10" s="14"/>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3920,6 +3920,53 @@
     </rPh>
     <rPh sb="131" eb="132">
       <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TICKETS-40　の作業中だと思いますが、いろいろ機能が混ざっているのでそれぞれサブタスクに切り分けた方がいいかもしれません。90分以内に終われるタスクに分解するのを目標にしてもらえるといいかもしれないです。</t>
+    <rPh sb="13" eb="16">
+      <t>サギョウチュウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ホウ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>プン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ブンカイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>モクヒョウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5034,8 +5081,12 @@
       <c r="C9" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
       <c r="A10" s="12">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3855,16 +3855,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・選択肢UIスクリプトの制作</t>
-    <rPh sb="1" eb="4">
-      <t>センタクシ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セイサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>自販機スクリプトのが完成したので、その続きで[F]入力で能力の選択肢UIが出るようにし、カーソルが乗ると選択肢の周りが黄色く表示されて、クリックするとDebug.Logが表示される選択肢UIスクリプトを制作中。
 イベントトリガーがごちゃごちゃにならないように気を付ける。</t>
     <rPh sb="0" eb="3">
@@ -3968,6 +3958,65 @@
     <rPh sb="86" eb="88">
       <t>モクヒョウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの制作
+　├スクリタブルオブジェクトでデータを作る✔
+　└データをランダムで三つ(重複なし)選択して表示させる</t>
+    <rPh sb="1" eb="4">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データを作れたので、そこからデータをランダムで重複せずに三つ表示させる作業中。
+リストを作ってシャッフルして取り出す方法に変更。</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ミッ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの制作
+　├スクリタブルオブジェクトでデータを作る✔
+　└データをランダムで三つ(重複なし)選択して表示させる</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5079,13 +5128,13 @@
         <v>85</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>88</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="108" customHeight="1">
@@ -5093,15 +5142,21 @@
         <v>46127</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="14"/>
+        <v>89</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>90</v>
+      </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="12"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="12">
+        <v>46128</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>91</v>
+      </c>
       <c r="C11" s="14"/>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="94">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4017,6 +4017,26 @@
     <t>・選択肢UIスクリプトの制作
 　├スクリタブルオブジェクトでデータを作る✔
 　└データをランダムで三つ(重複なし)選択して表示させる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・サブタスク分けもよくできています。その調子で進めていきましょう。</t>
+    <rPh sb="6" eb="7">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョウシ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>スス</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5147,8 +5167,12 @@
       <c r="C10" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
       <c r="A11" s="12">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="96">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4014,12 +4014,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・選択肢UIスクリプトの制作
-　├スクリタブルオブジェクトでデータを作る✔
-　└データをランダムで三つ(重複なし)選択して表示させる</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -4036,6 +4030,58 @@
     </rPh>
     <rPh sb="23" eb="24">
       <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの制作
+　├スクリタブルオブジェクトでデータを作る✔
+　├データをランダムで三つ(重複なし)選択して表示させる✔
+　└仮データを削除し、実際に使うデータの作成・表示✔</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リストを使ってスクリタブルオブジェクトのデータをUIに表示させるようにした。
+仮として表示させていたデータを実際に使うテキストや画像のデータを作り、表示できた。</t>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を実際のプロジェクトに実装させる</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5168,10 +5214,10 @@
         <v>90</v>
       </c>
       <c r="D10" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>92</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="108" customHeight="1">
@@ -5179,15 +5225,21 @@
         <v>46128</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="14"/>
+        <v>93</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>94</v>
+      </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="12"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="12">
+        <v>46129</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4082,6 +4082,35 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スクリプタブルオブジェクトを使いこなせると、もろもろ効率が良くなるので、積極的に使えると良いですね。</t>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウリツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>セッキョクテキ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>イ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5230,8 +5259,12 @@
       <c r="C11" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
       <c r="A12" s="12">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4073,19 +4073,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・自販機を実際のプロジェクトに実装させる</t>
-    <rPh sb="1" eb="4">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジッサイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -4111,6 +4098,106 @@
     </rPh>
     <rPh sb="45" eb="46">
       <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を実際のプロジェクトに実装させる✕
+・データの再設定
+・効果音検索(自販機・シャカ)</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>ジハンキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・効果音の実装</t>
+    <rPh sb="1" eb="4">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>α版までに缶に実装が間に合わなかったので後回しになった。
+要らない能力データの削除や新しく追加する強化等のデータの追加などをした。
+効果音を七個見つけてMP3ファイルをJiraに添付した。</t>
+    <rPh sb="1" eb="2">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>アトマワ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ナナコ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>テンプ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5260,10 +5347,10 @@
         <v>94</v>
       </c>
       <c r="D11" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="108" customHeight="1">
@@ -5271,15 +5358,21 @@
         <v>46129</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="14"/>
+        <v>97</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>99</v>
+      </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
-      <c r="A13" s="12"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>98</v>
+      </c>
       <c r="C13" s="14"/>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4198,6 +4198,32 @@
     </rPh>
     <rPh sb="89" eb="91">
       <t>テンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・飯沼さんも効果音をやっているようなので、作業内容が被らないように注意してやってください。</t>
+    <rPh sb="1" eb="3">
+      <t>イイヌマ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>サギョウナイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カブ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>チュウイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5363,8 +5389,12 @@
       <c r="C12" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="13"/>
+      <c r="D12" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="108" customHeight="1">
       <c r="A13" s="12">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="102">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3514,13 +3503,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・人形状のモデルが動かせるとわかりやすい技術アピールになるので重要です。
 ・指定の空オブジェクトを目指す仕組みができると、いろいろな演出に応用が効きそうですね。汎用的な仕組みを目指せるとさらに良いです。</t>
     <rPh sb="1" eb="4">
@@ -3914,13 +3896,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・TICKETS-40　の作業中だと思いますが、いろいろ機能が混ざっているのでそれぞれサブタスクに切り分けた方がいいかもしれません。90分以内に終われるタスクに分解するのを目標にしてもらえるといいかもしれないです。</t>
     <rPh sb="13" eb="16">
       <t>サギョウチュウ</t>
@@ -4014,13 +3989,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・サブタスク分けもよくできています。その調子で進めていきましょう。</t>
     <rPh sb="6" eb="7">
       <t>ワ</t>
@@ -4031,13 +3999,6 @@
     <rPh sb="23" eb="24">
       <t>スス</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・選択肢UIスクリプトの制作
-　├スクリタブルオブジェクトでデータを作る✔
-　├データをランダムで三つ(重複なし)選択して表示させる✔
-　└仮データを削除し、実際に使うデータの作成・表示✔</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -4069,13 +4030,6 @@
     </rPh>
     <rPh sb="74" eb="76">
       <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4132,16 +4086,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・効果音の実装</t>
-    <rPh sb="1" eb="4">
-      <t>コウカオン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>α版までに缶に実装が間に合わなかったので後回しになった。
 要らない能力データの削除や新しく追加する強化等のデータの追加などをした。
 効果音を七個見つけてMP3ファイルをJiraに添付した。</t>
@@ -4202,13 +4146,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・飯沼さんも効果音をやっているようなので、作業内容が被らないように注意してやってください。</t>
     <rPh sb="1" eb="3">
       <t>イイヌマ</t>
@@ -4224,6 +4161,232 @@
     </rPh>
     <rPh sb="33" eb="35">
       <t>チュウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェック</t>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの制作
+　├スクリタブルオブジェクトでデータを作る✔
+　├データをランダムで三つ(重複なし)選択して表示させる✔
+　└仮データを削除し、実際に使うデータの作成・表示✔</t>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの改造
+　├新しくデータを増やす(500ml)✔
+　└完全ランダムではなく確率・条件を利用したスクリプトに書き換え✔</t>
+    <rPh sb="12" eb="14">
+      <t>カイゾウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新しく一部の既存の上位互換のデータ(500ml)を作成した。
+すべてランダムではなく、効果が強いデータの排出確率が低くなるのと、下位互換と上位互換の両方が出ないようにスクリプトを書き換えた
+能力・強化表の最終版のエクセルをJiraに添付した。</t>
+    <rPh sb="0" eb="1">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチブ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キゾン</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>ジョウイゴカン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>コウカ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ハイシュツ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>カクリツ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="64" eb="68">
+      <t>カイゴカン</t>
+    </rPh>
+    <rPh sb="69" eb="73">
+      <t>ジョウイゴカン</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>リョウホウ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>デ</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>バン</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>テンプ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・選択肢UIスクリプトの改造
+　├効果音をつける(自販機のみ)✔
+　├自販機を実際のプロジェクトに配置
+　└缶スクリプトと紐づけ・実装</t>
+    <rPh sb="17" eb="20">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ヒモ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自販機に効果音を二個再生されるようにした。
+実際のプロジェクトに自販機を配置し、動作するようにした。
+UIのサイズ等が合わなくて修正に時間がかかってしまった。
+次回はすべての自販機設置ポイントに設置してNPC等の配置にすすむ</t>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニコ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サイセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ジカイ</t>
+    </rPh>
+    <rPh sb="87" eb="90">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を全設置ポイントに配置
+・NPCの実装</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4342,7 +4505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4363,6 +4526,11 @@
     <xf numFmtId="56" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5218,355 +5386,374 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="D2" s="4" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="108" customHeight="1">
-      <c r="A4" s="17">
+      <c r="A4" s="20">
         <v>46119</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" ht="108" customHeight="1">
-      <c r="A5" s="12">
+      <c r="A5" s="15">
         <v>46120</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
-      <c r="A6" s="12">
+      <c r="A6" s="15">
         <v>46121</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="14" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="108" customHeight="1">
+      <c r="A7" s="15">
+        <v>46122</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="108" customHeight="1">
-      <c r="A7" s="12">
-        <v>46122</v>
-      </c>
-      <c r="B7" s="14" t="s">
+    <row r="8" spans="1:5" ht="108" customHeight="1">
+      <c r="A8" s="15">
+        <v>46125</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="15" t="s">
+      <c r="C8" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="108" customHeight="1">
-      <c r="A8" s="12">
-        <v>46125</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="E8" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="15" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="108" customHeight="1">
+      <c r="A9" s="15">
+        <v>46126</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="108" customHeight="1">
-      <c r="A9" s="12">
-        <v>46126</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="E9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="15" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="108" customHeight="1">
+      <c r="A10" s="15">
+        <v>46127</v>
+      </c>
+      <c r="B10" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="C10" s="17" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="108" customHeight="1">
-      <c r="A10" s="12">
-        <v>46127</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="D10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="14" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="108" customHeight="1">
+      <c r="A11" s="15">
+        <v>46128</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="13" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="108" customHeight="1">
+      <c r="A12" s="15">
+        <v>46129</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="108" customHeight="1">
-      <c r="A11" s="12">
-        <v>46128</v>
-      </c>
-      <c r="B11" s="14" t="s">
+      <c r="C12" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D12" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="108" customHeight="1">
-      <c r="A12" s="12">
-        <v>46129</v>
-      </c>
-      <c r="B12" s="14" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="108" customHeight="1">
+      <c r="A13" s="15">
+        <v>46132</v>
+      </c>
+      <c r="B13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C13" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" spans="1:5" ht="108" customHeight="1">
+      <c r="A14" s="15">
+        <v>46133</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="1:5" ht="108" customHeight="1">
+      <c r="A15" s="15">
+        <v>46134</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="108" customHeight="1">
-      <c r="A13" s="12">
-        <v>46132</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" ht="108" customHeight="1">
-      <c r="A14" s="12"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:5" ht="108" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="13"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="12"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="13"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
-      <c r="A18" s="12"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
-      <c r="A19" s="12"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="16"/>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
-      <c r="A20" s="12"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="13"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" ht="108" customHeight="1">
-      <c r="A22" s="12"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" ht="108" customHeight="1">
-      <c r="A23" s="12"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24" spans="1:5" ht="108" customHeight="1">
-      <c r="A24" s="12"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25" spans="1:5" ht="108" customHeight="1">
-      <c r="A25" s="12"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="16"/>
     </row>
     <row r="26" spans="1:5" ht="108" customHeight="1">
-      <c r="A26" s="12"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="13"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="16"/>
     </row>
     <row r="27" spans="1:5" ht="108" customHeight="1">
-      <c r="A27" s="12"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28" spans="1:5" ht="108" customHeight="1">
-      <c r="A28" s="12"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="13"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="16"/>
     </row>
     <row r="29" spans="1:5" ht="108" customHeight="1">
-      <c r="A29" s="12"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30" spans="1:5" ht="108" customHeight="1">
-      <c r="A30" s="12"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31" spans="1:5" ht="108" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32" spans="1:5" ht="108" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="16"/>
     </row>
     <row r="33" spans="1:5" ht="108" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="16"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="1:5" ht="108" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="13"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="35" spans="1:5" ht="108" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36" spans="1:5" ht="108" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="13"/>
+      <c r="A36" s="15"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -4279,37 +4279,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・選択肢UIスクリプトの改造
-　├効果音をつける(自販機のみ)✔
-　├自販機を実際のプロジェクトに配置
-　└缶スクリプトと紐づけ・実装</t>
-    <rPh sb="17" eb="20">
-      <t>コウカオン</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="35" eb="38">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>ジッサイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="54" eb="55">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="61" eb="62">
-      <t>ヒモ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>自販機に効果音を二個再生されるようにした。
 実際のプロジェクトに自販機を配置し、動作するようにした。
 UIのサイズ等が合わなくて修正に時間がかかってしまった。
@@ -4371,8 +4340,40 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・自販機を全設置ポイントに配置
-・NPCの実装</t>
+    <t>・選択肢UIスクリプトの改造
+　├効果音をつける(自販機のみ)✔
+　├自販機を実際のプロジェクトに配置✔
+　└缶スクリプトと紐づけ・実装✔</t>
+    <rPh sb="17" eb="20">
+      <t>コウカオン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="35" eb="38">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ジッサイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ヒモ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・自販機を全設置ポイントに配置
+・NPCの実装
+</t>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
     </rPh>
@@ -5589,10 +5590,10 @@
         <v>46133</v>
       </c>
       <c r="B14" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>100</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="103">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4371,9 +4371,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">・自販機を全設置ポイントに配置
-・NPCの実装
-</t>
+    <t>・自販機を全設置ポイントに配置</t>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
     </rPh>
@@ -4386,8 +4384,40 @@
     <rPh sb="13" eb="15">
       <t>ハイチ</t>
     </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジッソウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自販機半分以上は設置できた。
+自販機で飲み物選択中に缶を操作できないようにした。</t>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンブン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>センタクチュウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ソウサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5605,7 +5635,9 @@
       <c r="B15" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="17"/>
+      <c r="C15" s="17" t="s">
+        <v>102</v>
+      </c>
       <c r="D15" s="18"/>
       <c r="E15" s="16"/>
     </row>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4388,6 +4388,29 @@
     </rPh>
     <rPh sb="21" eb="23">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・進捗と、予定の記載をお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5606,8 +5629,12 @@
         <v>101</v>
       </c>
       <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
       <c r="A16" s="15"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7905" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="サンプル" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="108">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4371,6 +4371,29 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・進捗と、予定の記載をお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>シンチョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・自販機を全設置ポイントに配置</t>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
@@ -4388,7 +4411,7 @@
   </si>
   <si>
     <t>自販機半分以上は設置できた。
-自販機で飲み物選択中に缶を操作できないようにした。</t>
+自販機で飲み物選択中に缶を操作できないようにスクリプトを変更した。</t>
     <rPh sb="0" eb="3">
       <t>ジハンキ</t>
     </rPh>
@@ -4418,6 +4441,104 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>ソウサ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・残りの設置ポイントに自販機を設置</t>
+    <rPh sb="1" eb="2">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設置してGitに投稿した際に不具合が発生したため昨日と二時限目の設置がパぁ↑になった。
+別プロジェクトにある自販機プレハブのUIを直した上で本プロジェクトに貼り付けた</t>
+    <rPh sb="0" eb="2">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウコウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>ニジゲンメ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・残りの設置ポイントに自販機を設置
+・自販機購入時缶がアップグレードされるように紐づけさせる</t>
+    <rPh sb="1" eb="2">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>コウニュウジ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ヒモ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5633,24 +5754,38 @@
         <v>46134</v>
       </c>
       <c r="B15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="15">
+        <v>46135</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>106</v>
+      </c>
       <c r="D16" s="18"/>
       <c r="E16" s="16"/>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="15">
+        <v>46136</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>107</v>
+      </c>
       <c r="C17" s="17"/>
       <c r="D17" s="18"/>
       <c r="E17" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4371,27 +4371,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">・自販機を全設置ポイントに配置
-・NPCの実装
-</t>
-    <rPh sb="1" eb="4">
-      <t>ジハンキ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>セッチ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ハイチ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ジッソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -4411,6 +4390,129 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を全設置ポイントに配置
+・スクリプトを修正</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>半分以上は設置できたので引き続き設置を進める
+選択中に動けてしまうのを修正した</t>
+    <rPh sb="0" eb="4">
+      <t>ハンブンイジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツヅ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>センタクチュウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機を全設置ポイントに設置</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設置できてGitに上げたのですが、プレハブが壊れたりフォントが消えたりデータが飛んだりで不具合が発生したため、再設置・UIサイズの修正をやり直すことになった</t>
+    <rPh sb="0" eb="2">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="44" eb="47">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="55" eb="58">
+      <t>サイセッチ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>ナオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・自販機設置
+・スクリプトの修正
+・缶スクリプトのステータス反映</t>
+    <rPh sb="1" eb="4">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ハンエイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5626,26 +5728,42 @@
         <v>46134</v>
       </c>
       <c r="B15" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="16" spans="1:5" ht="108" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="16"/>
+      <c r="A16" s="15">
+        <v>46135</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="108" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="15">
+        <v>46136</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>107</v>
+      </c>
       <c r="C17" s="17"/>
       <c r="D17" s="18"/>
       <c r="E17" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4496,9 +4496,78 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>自販機の設置が完了し、選択中にタイマーが進まなくするのと、ポーズを開けないようにスクリプトを修正した。
+強化自販機で飲み物選択した時ステータスが強化されるようにした。
+提出直前Gitでデータが飛んだため、本プロジェクトのほうでは実装されてない状態のデータを提出という形になりました。</t>
+    <rPh sb="0" eb="3">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>センタクチュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="54" eb="57">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>モノセンタク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="102" eb="103">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>カタチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>・自販機設置
 ・スクリプトの修正
-・缶スクリプトのステータス反映</t>
+・缶スクリプトのステータス強化反映</t>
     <rPh sb="1" eb="4">
       <t>ジハンキ</t>
     </rPh>
@@ -4512,6 +4581,22 @@
       <t>カン</t>
     </rPh>
     <rPh sb="30" eb="32">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・缶スクリプトの能力反映</t>
+    <rPh sb="1" eb="2">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
       <t>ハンエイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -5762,15 +5847,21 @@
         <v>46136</v>
       </c>
       <c r="B17" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="17"/>
       <c r="D17" s="18"/>
       <c r="E17" s="16"/>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
-      <c r="A18" s="15"/>
-      <c r="B18" s="17"/>
+      <c r="A18" s="15">
+        <v>46139</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>109</v>
+      </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
       <c r="E18" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="112">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4598,6 +4598,36 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・状況承知しました。
+・Gitのデータが飛ぶ現象の原因を究明した方がいいかもしれないです。</t>
+    <rPh sb="1" eb="5">
+      <t>ジョウキョウショウチ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ゲンショウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ゲンイン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キュウメイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ホウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5852,8 +5882,12 @@
       <c r="C17" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
       <c r="A18" s="15">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4589,19 +4589,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・缶スクリプトの能力反映</t>
-    <rPh sb="1" eb="2">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ノウリョク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -4628,6 +4615,82 @@
     </rPh>
     <rPh sb="32" eb="33">
       <t>ホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本プロジェクトに自販機のデータの転送が成功しました
+アニメーションイベントで缶が吹っ飛ぶようにした
+SEも追加した</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・Gitデータ転送リベンジ
+・NPCの缶蹴り実装
+・蹴った時の音、足音の実装</t>
+    <rPh sb="7" eb="9">
+      <t>テンソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンケ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>アシオト</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・本プロジェクトにNPCの蹴り等実装</t>
+    <rPh sb="1" eb="2">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5883,10 +5946,10 @@
         <v>107</v>
       </c>
       <c r="D17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>110</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="108" customHeight="1">
@@ -5894,15 +5957,21 @@
         <v>46139</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="17"/>
+        <v>112</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>111</v>
+      </c>
       <c r="D18" s="18"/>
       <c r="E18" s="16"/>
     </row>
     <row r="19" spans="1:5" ht="108" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="17"/>
+      <c r="A19" s="15">
+        <v>46140</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>113</v>
+      </c>
       <c r="C19" s="17"/>
       <c r="D19" s="18"/>
       <c r="E19" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4691,6 +4691,20 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・作業報告と翌日の作業予定の記載をお願いします。</t>
+    <rPh sb="1" eb="5">
+      <t>サギョウホウコク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5973,8 +5987,12 @@
         <v>113</v>
       </c>
       <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="16"/>
+      <c r="D19" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="108" customHeight="1">
       <c r="A20" s="15"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4679,7 +4679,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・本プロジェクトにNPCの蹴り等実装</t>
+    <t>・本プロジェクトにNPCの蹴り等実装
+・データの画像の修正
+・ステータスUIの実装</t>
     <rPh sb="1" eb="2">
       <t>ホン</t>
     </rPh>
@@ -4692,19 +4694,160 @@
     <rPh sb="16" eb="18">
       <t>ジッソウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>蒲池</t>
-    <rPh sb="0" eb="2">
-      <t>カマチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>・作業報告と翌日の作業予定の記載をお願いします。</t>
-    <rPh sb="1" eb="5">
-      <t>サギョウホウコク</t>
+    <rPh sb="24" eb="26">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蹴りを本プロジェクトに実装した
+ステータスUIがレベルに合わせて変化するようにした
+データの画像がマージできていないことに気づき、画像を更新した</t>
+    <rPh sb="0" eb="1">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・マウスカーソルの表示・非表示の修正
+・UIの"Gage"を”Gauge”に修正
+・NPCの足音の大きさ調整
+・木のコライダー変更
+・自販機のバグ修正</t>
+    <rPh sb="9" eb="11">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ヒヒョウジ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>アシオト</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="67" eb="70">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マウスカーソルの修正が完了した
+UIのスペルも直してNPCの足音の大きさと聞こえる範囲を調整した
+木の葉っぱの当たり判定をなくすため新しくコライダーをつけた
+ポーズ中に自販機で購入できてしまうバグを修正した</t>
+    <rPh sb="8" eb="10">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>アシオト</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="84" eb="87">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・要らないデータの削除
+・ビルドした状態でのデバック</t>
+    <rPh sb="1" eb="2">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5986,24 +6129,32 @@
       <c r="B19" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18" t="s">
+      <c r="C19" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="D19" s="18"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="1:5" ht="108" customHeight="1">
+      <c r="A20" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="108" customHeight="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="C20" s="17" t="s">
+        <v>116</v>
+      </c>
       <c r="D20" s="18"/>
       <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="15">
+        <v>46150</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>117</v>
+      </c>
       <c r="C21" s="17"/>
       <c r="D21" s="18"/>
       <c r="E21" s="16"/>

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="120">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4848,6 +4848,42 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・予定通りの進行で来ているようで何よりです。
+・不要データの削除とデバッグも大切なのでよろしくお願いします。</t>
+    <rPh sb="1" eb="4">
+      <t>ヨテイドオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タイセツ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6145,8 +6181,12 @@
       <c r="C20" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="16"/>
+      <c r="D20" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
       <c r="A21" s="15">

--- a/Reports/05_saiwaki_ren_作業報告.xlsx
+++ b/Reports/05_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -4838,20 +4838,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・要らないデータの削除
-・ビルドした状態でのデバック</t>
-    <rPh sb="1" eb="2">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>蒲池</t>
     <rPh sb="0" eb="2">
       <t>カマチ</t>
@@ -4884,6 +4870,78 @@
     </rPh>
     <rPh sb="48" eb="49">
       <t>ネガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・UI・NPC・自販機の再マージ
+・車SEの修正
+・要らないデータの削除✕
+・ビルドした状態でのデバック✕</t>
+    <rPh sb="8" eb="11">
+      <t>ジハンキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>昨日の放課後に失敗したデータを再マージしたが失敗したため人力で追加
+ポーズ中に車の音が鳴るのを修正したがマージ失敗</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ホウカゴ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジンリキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>クルマ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オト</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6182,10 +6240,10 @@
         <v>116</v>
       </c>
       <c r="D20" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>118</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="108" customHeight="1">
@@ -6193,9 +6251,11 @@
         <v>46150</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C21" s="17"/>
+        <v>119</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>120</v>
+      </c>
       <c r="D21" s="18"/>
       <c r="E21" s="16"/>
     </row>
